--- a/output/第10期計画_キックオフ会議議事録の校正結果.xlsx
+++ b/output/第10期計画_キックオフ会議議事録の校正結果.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -842,33 +842,33 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>提案</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>表記</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>5. ③ KPI・役割分担</t>
+          <t>2. 計画の位置付け</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>本文KPI12＋補完4</t>
+          <t>介護人材、保険事業運営を持続可能なものとする</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>「代表KPI16項目（うち補完4項目）」</t>
+          <t>介護人材、介護保険事業の運営を持続可能なものとする</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>内容は同じである（12＋4＝16）。ただし「本文KPI12」と「補完4」が別枠と読める余地があるため、計画骨子案及びKPI定義書の表記に揃えることを提案する。原本の記載を変えることになるため反映していない。</t>
+          <t>「保険事業運営」は生命保険等で用いる語である。「福祉の中でも上位に位置する計画」はご指示によりそのままとした。</t>
         </is>
       </c>
     </row>
@@ -876,119 +876,119 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>提案</t>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>表記</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>2. 計画の位置付け</t>
+          <t>5. ③ KPI・役割分担</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>保険事業運営</t>
+          <t>本文KPI12＋補完4、5基本目標、広域連合と3町の責任分担</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>「介護保険事業の運営」</t>
+          <t>代表KPI16項目（うち補完4項目）、5基本目標、広域連合と3町の責任分担。アンケートは現在実施したもので完了のため、現在のデータでは算定できない4項目（H07・H08・H12・H16）は、代理指標への振替え又は項目の削除を検討する</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>「保険事業運営」は生命保険等で用いる語であり、介護保険では通常「介護保険事業の運営」又は「保険者としての運営」と表す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
+          <t>計画骨子案及びKPI定義書の表記に揃えた。あわせて、算定できない4項目の扱いをご指示により追記した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>提案</t>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>表記</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>2. 計画の位置付け</t>
+          <t>2. 重点論点</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>福祉の中でも上位に位置する計画</t>
+          <t>３町の議員が同席する中で報告を行うため、３町の特異性を平準化させることに留意する。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>「市町村介護保険事業計画として、構成3町の老人福祉計画と一体的に作成する計画」</t>
+          <t>３町の議員が同席する中で報告を行うため、３町の差を把握したうえで、広域として共通の施策体系に整理することに留意する。</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画は、老人福祉計画と一体のものとして作成し、市町村地域福祉計画等と調和が保たれたものでなければならない（介護保険法第117条）。「福祉の中でも上位」とすると、3町の地域福祉計画との関係を説明できなくなる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>「特異性を平準化」は、地域差を均すとも様式を揃えるとも読める。地域差は把握して施策に反映する対象であるため、意味を特定した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>要協議①</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>3-3. サービス見込量・保険料</t>
+          <t>3-1. 現状分析・将来推計</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>「〜します」（敬体）</t>
+          <t>XMLの断片（3-1. 現状分析・将来推計）</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>「〜する」（常体）</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>3-1・3-2は常体、3-3のみ敬体である。議事録の文体を統一する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+          <t>会議での発言をそのまま記載したものであり、方針は「総合戦略をベースに補正を行う」であるとのご指示による。2. 基礎データの「人口推計のカーブを参考に補正を行うことを確認」と表現を揃えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>要協議②</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>3-4. 推進協議会・パブリックコメント</t>
+          <t>3-1. 現状分析・将来推計</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>「第2回協議会」</t>
+          <t>XMLの断片（3-1. 現状分析・将来推計）</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>「第1回」の記載の追加、又は「委員会」との呼称の統一</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>第2回の前に第1回の記載がない。また4. の表では「第1回委員会資料」とあり、「委員会」と「協議会」の呼称が混在している。</t>
+          <t>給付費に効くのは65歳以上・75歳以上である。総人口では住民基本台帳が社人研推計を622人上回る一方、65歳以上では144人、75歳以上では256人下回っており、向きが逆である。</t>
         </is>
       </c>
     </row>
@@ -998,27 +998,27 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>要協議③</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>3-4. 10月構成町意見照会</t>
+          <t>3-3. 本文</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>段階名「10月構成町意見照会」／時期「10〜11月頃」</t>
+          <t>XMLの断片（3-3. 本文）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>段階名と時期を一致させる</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>段階名が10月、時期が10〜11月頃で食い違っている。</t>
+          <t>「令和8年実績」を「年報・月報」に改めるとのご指示による。あわせて、3-1・3-2が常体であるため文体を揃えた。</t>
         </is>
       </c>
     </row>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>要協議③</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>3-4. パブリックコメント</t>
+          <t>3-3. 手順2</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>想定内容欄と時期・状態欄</t>
+          <t>令和8年実績で人口・認定・受給・給付を再基準化</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>重複の解消</t>
+          <t>年報・月報の実績で人口・認定・受給・給付を再基準化</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>「令和9年1月に概要版を用いWEBにて2週間実施」が2つの欄に重複して記載されている。</t>
+          <t>上に同じ。</t>
         </is>
       </c>
     </row>
@@ -1058,237 +1058,537 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>要協議③</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>3-4. 最終報告・答申</t>
+          <t>4. 令和8年10月</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>「主監会議」</t>
+          <t>令和8年実績で再基準化、供給制約分析</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>正式名称の確認</t>
+          <t>年報・月報の実績で再基準化、供給制約分析</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>「主監会議」の正式名称を確認のうえ表記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
+          <t>上に同じ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>要協議③</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>2. 重点論点</t>
+          <t>5. ④ 再基準化・シナリオ</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>「３町の特異性を平準化させる」</t>
+          <t>令和8年実績を起点に自然体・需要上振れ・供給制約・基金反映を比較</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>「3町の差を把握したうえで、広域として共通の施策体系に整理する」</t>
+          <t>年報・月報の実績を起点に自然体・需要上振れ・供給制約・基金反映を比較</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>「平準化」は3町の地域差を均すとも、様式を揃えるとも読める。当方は地域差の分析（第10期計画_地域差の分析.xlsx）を実施済みであり、地域差は把握して施策に反映する対象である。本文の記述と齟齬が生じないよう、意味を特定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="91" customHeight="1">
+          <t>上に同じ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="39" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>要協議④</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>3-1. 現状分析・将来推計</t>
+          <t>2. 保険料</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>「人口推計は地方創生計画による人口推計の値を使用」</t>
+          <t>XMLの断片（2. 保険料）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>3町一律には適用できない。第3期総合戦略の総人口目標は、東神楽町が「令和11年度までに9,500人維持」、東川町が8,635人、美瑛町は総人口目標を設定していない。令和7年国勢調査（速報）は東神楽町9,588人・東川町8,726人・美瑛町9,337人で、東川町は目標を91人上回っている一方、東神楽町は年▲1.09％のペースで令和8年中に9,500人を割る見込みである。美瑛町は使用する目標値が存在しない。議事録の記載のままでは、町ごとに扱いが異なることが読み取れない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="91" customHeight="1">
+          <t>農業収入が高かったことは事実である一方、それが基金の取り崩しが少なかった理由であるかは確かめていないため、因果を切り離し、事実の記載にとどめるとのご指示による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>要協議⑥</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>3-1. 現状分析・将来推計</t>
+          <t>5. ① 調査データの受渡し</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>「社人研の自然推計を元にした見える化システムとの乖離を確認する」</t>
+          <t>事業所実態調査の回答データの受渡し方法、集計単位、公表単位</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>事業所実態調査の回答データは受領済み。集計単位、公表単位を確認する</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>方向は妥当であるが、総人口の乖離だけを見ると判断を誤る。社人研推計（見える化A1）の令和7年値と国勢調査（速報）の実績の差は、東川町＋513人・美瑛町＋444人・東神楽町▲408人で町ごとに向きが異なる。一方、住民基本台帳（令和8年）との突合では、総人口は住基が622人多いのに、65歳以上は144人、75歳以上は256人少ない。給付費に効くのは65歳以上・75歳以上であり、突合はこの2区分で行う必要がある（第10期計画_世帯構成の突合.xlsx 06シート）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="52" customHeight="1">
+          <t>令和8年8月6日に「現時点で提出いただいている調査結果のすべて」として受領済みであるとのご指示による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="39" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>表記</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>3-3. サービス見込量・保険料　手順2</t>
+          <t>3-4. 10月構成町意見照会</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>「令和8年実績で再基準化」（8〜9月）</t>
+          <t>XMLの断片（3-4. 10月構成町意見照会）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>令和8年度は第9期の最終年度であり、実績が確定するのは令和9年3月末である。8〜9月の時点で用いられるのは令和7年度実績と令和8年度の月報までである。「令和8年実績」が令和8年度の実績を指すのか、令和8年（暦年）時点で得られる直近実績を指すのかを特定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="104" customHeight="1">
+          <t>段階名が「10月」、時期欄が「10〜11月頃」で食い違っていた。また第2回の前に第1回の記載がなかった。調査結果報告・現状分析・骨子案を扱う回であり、第1回協議会に当たるものとして段階名を改めた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>表記</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2. 保険料</t>
+          <t>3-4. パブリックコメント</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>「第10期保険料は現行水準の据え置きを目標とする」</t>
+          <t>XMLの断片（3-4. パブリックコメント）</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>反映済み</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>現行（第9期）の基準額は月額6,400円である。見える化システムの自然体推計による第10期の3年平均は6,238円（基金取崩0円・予定収納率99.0％）で、現行を162円下回る。据え置きは現時点で無理のない目標であるが、第3段階（給付費・保険料）の推計は単価・基金残高・収納率・所得段階別被保険者数の受領後に確定する。また「米価の上昇により農業収入が高かったため基金の取崩しがなかった」という因果は確かめられていない。給付費が想定を下回った可能性もあるため、議事録では「基金の取崩しは想定を下回った」という事実の記載にとどめることを提案する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="91" customHeight="1">
+          <t>想定内容欄と時期・状態欄に「令和9年1月に概要版を用いWEBにて2週間実施」が重複して記載されていた。想定内容欄から日程を外した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>表記</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>5. ③ KPI・役割分担（☑確認）</t>
+          <t>4. 令和8年8月上旬</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>代表KPI4項目の代理指標が未決である</t>
+          <t>計画素案、第1回委員会資料、KPI定義書</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>計画素案、第1回協議会資料、KPI定義書</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>受領済みの調査には、H12（必要サービス未充足率）の受入困難の設問と、H16（災害・感染症時のサービス継続率）のBCPの設問が含まれていない。H07（主介護者の高負担割合）・H08（介護離職懸念）は在宅介護実態調査によるもので、同調査は実施していない。この4項目は現在のデータでは算定できない。「確認」で閉じると、基準値のないKPIが計画に残る。代理指標への振替え、項目の削除、又は2問の追加照会のいずれかを決定する必要がある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="78" customHeight="1">
+          <t>「委員会」と「協議会」が混在していたため「協議会」に統一した。正式名称は要確認である（当方の成果品では「策定委員会」と表記している）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>表記</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>5. ① 調査データの受渡し（☑確認）</t>
+          <t>5. ⑤ 会議・公開</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>事業所実態調査は受領済みである</t>
+          <t>委員会の審議順、町別値・事業所情報の公開範囲</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
+          <t>協議会の審議順、町別値・事業所情報の公開範囲</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>上に同じ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>2. 基礎データ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>３町の地方創生計画にある人口推計のカーブ</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>３町の地方創生総合戦略にある人口推計のカーブ</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>3-1及び3-3を「地方創生総合戦略」に改めたため、文書内の呼称を揃えた。3町の計画の正式名称は「第3期（写真文化首都／美瑛町）まち・ひと・しごと創生総合戦略」である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>見送り</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>2. 計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>福祉の中でも上位に位置する計画</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>（ご指示によりそのまま）</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業計画は、老人福祉計画と一体のものとして作成し、市町村地域福祉計画等と調和が保たれたものとされる（介護保険法第117条）。「福祉の中でも上位」とすると3町の地域福祉計画との関係を説明しにくくなるが、令和8年8月6日のご指示により原本のままとした。計画本文（第1章第1節）に同じ表現を用いる場合は、改めてご相談したい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>3-4. 最終報告・答申</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>「主監会議」</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>正式名称の確認</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>当方では正式名称を確認できないため、原本のままとした。「主幹会議」の誤りである可能性もあるため、ご確認をお願いしたい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="39" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>3-4／4／5</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>「協議会」と「委員会」の呼称</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>議事録内は「協議会」に統一</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>議事録内では3-4の表題（推進協議会）に合わせて「協議会」に統一した。ただし当方の成果品では「策定委員会」と表記しており、正式名称の確認を要する。確定後、当方の成果品側も揃える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="104" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>反映済①</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>3-1. 現状分析・将来推計</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>総合戦略をベースに補正を行う</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>令和8年8月6日に「現時点で提出いただいている調査結果のすべて」として受領済みであり、受渡し方法を確認する段階ではない。受領した回答は事業所票27件・職員個票317人・訪問系職員票26件で、訪問系は13事業所のうち3事業所からの回答である（残る10事業所は介護サービス情報公表システムの個別公表画面により把握済み）。記載を実態に合わせることを提案する。</t>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>ご指示のとおり「３町の地方創生総合戦略の人口推計をベースに補正を行う」に改めた。町ごとの扱いは、補正の作業の中で次のとおり整理する。第3期総合戦略の総人口目標は東神楽町が令和11年度9,500人維持、東川町が8,635人、美瑛町は設定なしである。令和7年国勢調査（速報）は東神楽町9,588人・東川町8,726人・美瑛町9,337人で、東川町は目標を91人上回る一方、東神楽町は年▲1.09％のペースで令和8年中に9,500人を割る見込みである。美瑛町はベースとする目標値がないため、国勢調査及び社人研推計による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="78" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>反映済②</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>3-1. 現状分析・将来推計</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>乖離の確認は65歳以上・75歳以上で行う</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>ご指示のとおり本文に追記した。社人研推計（見える化A1）の令和7年値と国勢調査（速報）の実績の差は、東川町＋513人・美瑛町＋444人・東神楽町▲408人で町ごとに向きが異なる。一方、住民基本台帳（令和8年）との突合では、総人口は住基が622人多いのに、65歳以上は144人、75歳以上は256人少ない。（第10期計画_世帯構成の突合.xlsx 06シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="39" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>反映済③</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>3-3／4／5</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>「令和8年実績」を「年報・月報」に</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>ご指示のとおり4か所を改めた。令和8年度は第9期の最終年度であり実績の確定は令和9年3月末となるため、8〜9月の再基準化には年報・月報の直近実績を用いる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="91" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>反映済④</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>2. 保険料</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>農業収入と基金の因果を切り離す</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>ご指示のとおり「米の価格が上昇し、農業収入は高かった。また、基金の取り崩しは想定を下回った。」に改めた。なお現行（第9期）の基準額は月額6,400円、見える化システムの自然体推計による第10期の3年平均は6,238円（基金取崩0円・予定収納率99.0％）で、現行を162円下回る。据え置きは現時点で無理のない目標である。第3段階（給付費・保険料）の推計は、単価・基金残高・収納率・所得段階別被保険者数の受領後に確定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="104" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>反映済⑤</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>5. ③ KPI・役割分担</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>代理指標への振替え又は項目の削除を検討</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>ご指示のとおり追記した。対象は代表KPIのうちH07（主介護者の高負担割合）・H08（介護離職懸念）・H12（必要サービス未充足率）・H16（災害・感染症時のサービス継続率）の4項目である。H07・H08は在宅介護実態調査、H12は事業所調査の受入困難の設問、H16は同調査のBCPの設問を要するが、いずれも実施していない。振替えの候補は、H12を居所変更実態調査の「供給不足を理由とする住替え」、H16をBCP策定率（公表システムから把握可）とすることが考えられる。次回の打合せまでに振替え案を整理して提示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="65" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>反映済⑥</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>5. ① 調査データの受渡し</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>受領済みへ修正</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>ご指示のとおり「回答データは受領済み。集計単位、公表単位を確認する」に改めた。受領した回答は事業所票27件・職員個票317人・訪問系職員票26件である。訪問系は13事業所のうち3事業所からの回答であり、残る10事業所は介護サービス情報公表システムの個別公表画面により把握済みである（訪問介護員等は13事業所で181人）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_キックオフ会議議事録の校正結果.xlsx
+++ b/output/第10期計画_キックオフ会議議事録の校正結果.xlsx
@@ -1356,9 +1356,9 @@
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>解決済</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>「主監会議」</t>
+          <t>「事務管理者・主監会議」</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>正式名称の確認</t>
+          <t>原本のまま（修正不要）</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>当方では正式名称を確認できないため、原本のままとした。「主幹会議」の誤りである可能性もあるため、ご確認をお願いしたい。</t>
+          <t>令和8年8月6日のご指示により、発注者側の資料からの抜粋であることを確認した。表記はこのままとする。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_キックオフ会議議事録の校正結果.xlsx
+++ b/output/第10期計画_キックオフ会議議事録の校正結果.xlsx
@@ -506,7 +506,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>誤字脱字及び明らかな表記の誤りは「第10期計画_キックオフ会議議事録_校正反映.odt」に反映済みである。「提案」及び「要協議」は反映していない。</t>
+          <t>誤字脱字及び明らかな表記の誤りは「第10期計画_キックオフ会議議事録_令和8年8月6日.odt」に反映済みである。「提案」及び「要協議」は反映していない。</t>
         </is>
       </c>
     </row>
